--- a/docs/sample-data/sample-rpti-2027.xlsx
+++ b/docs/sample-data/sample-rpti-2027.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -911,22 +911,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Legacy Teller Application</v>
+        <v>Primary Data Center Jakarta</v>
       </c>
       <c r="C13" t="str">
-        <v>Branch teller front-end modernisation.</v>
+        <v>Add two floors of rack capacity to the existing facility.</v>
       </c>
       <c r="D13" t="str">
-        <v>Internal management</v>
+        <v>Data Center / Disaster Recovery Center</v>
       </c>
       <c r="E13" t="str">
         <v>upgrade</v>
       </c>
       <c r="F13" t="str">
-        <v>inhouse</v>
+        <v>PPJTI</v>
       </c>
       <c r="G13" t="str">
-        <v>n/a</v>
+        <v>no</v>
       </c>
       <c r="H13" t="str">
         <v>Jakarta, Indonesia</v>
@@ -938,18 +938,59 @@
         <v>Q3</v>
       </c>
       <c r="K13">
+        <v>7400000000</v>
+      </c>
+      <c r="L13">
+        <v>1900000000</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Existing DC; not an LKPTI item.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Legacy Teller Application</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Branch teller front-end modernisation.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Internal management</v>
+      </c>
+      <c r="E14" t="str">
+        <v>upgrade</v>
+      </c>
+      <c r="F14" t="str">
+        <v>inhouse</v>
+      </c>
+      <c r="G14" t="str">
+        <v>n/a</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Jakarta, Indonesia</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Surabaya, Indonesia</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="K14">
         <v>2900000000</v>
       </c>
-      <c r="L13">
+      <c r="L14">
         <v>640000000</v>
       </c>
-      <c r="M13" t="str">
+      <c r="M14" t="str">
         <v>Not present in the 2026 LKPTI — needs a target.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/docs/sample-data/sample-rpti-2027.xlsx
+++ b/docs/sample-data/sample-rpti-2027.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="36.83203125" customWidth="1"/>
@@ -665,22 +665,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Digital Onboarding (eKYC)</v>
+        <v>Open API Banking Platform</v>
       </c>
       <c r="C7" t="str">
-        <v>Remote account opening with liveness and Dukcapil verification.</v>
+        <v>Scale partner API capacity and add consent-management controls.</v>
       </c>
       <c r="D7" t="str">
-        <v>Customer management</v>
+        <v>Digital services</v>
       </c>
       <c r="E7" t="str">
-        <v>new</v>
+        <v>upgrade</v>
       </c>
       <c r="F7" t="str">
-        <v>PPJTI</v>
+        <v>inhouse</v>
       </c>
       <c r="G7" t="str">
-        <v>no</v>
+        <v>n/a</v>
       </c>
       <c r="H7" t="str">
         <v>Jakarta, Indonesia</v>
@@ -689,16 +689,16 @@
         <v>Surabaya, Indonesia</v>
       </c>
       <c r="J7" t="str">
-        <v>Q2</v>
+        <v>Q3</v>
       </c>
       <c r="K7">
-        <v>5400000000</v>
+        <v>3600000000</v>
       </c>
       <c r="L7">
-        <v>980000000</v>
+        <v>720000000</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>Partner API phase 2 capacity upgrade.</v>
       </c>
     </row>
     <row r="8">
@@ -706,13 +706,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Syariah Financing Module</v>
+        <v>Digital Onboarding (eKYC)</v>
       </c>
       <c r="C8" t="str">
-        <v>Murabahah and musyarakah financing administration.</v>
+        <v>Remote account opening with liveness and Dukcapil verification.</v>
       </c>
       <c r="D8" t="str">
-        <v>Credit / financing</v>
+        <v>Customer management</v>
       </c>
       <c r="E8" t="str">
         <v>new</v>
@@ -730,16 +730,16 @@
         <v>Surabaya, Indonesia</v>
       </c>
       <c r="J8" t="str">
-        <v>Q4</v>
+        <v>Q2</v>
       </c>
       <c r="K8">
-        <v>9700000000</v>
+        <v>5400000000</v>
       </c>
       <c r="L8">
-        <v>1100000000</v>
+        <v>980000000</v>
       </c>
       <c r="M8" t="str">
-        <v>Supports the planned syariah business unit.</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -747,13 +747,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>DRC Site Relocation — Surabaya</v>
+        <v>Syariah Financing Module</v>
       </c>
       <c r="C9" t="str">
-        <v>Move the disaster recovery site to a Tier III facility.</v>
+        <v>Murabahah and musyarakah financing administration.</v>
       </c>
       <c r="D9" t="str">
-        <v>Data Center / Disaster Recovery Center</v>
+        <v>Credit / financing</v>
       </c>
       <c r="E9" t="str">
         <v>new</v>
@@ -771,16 +771,16 @@
         <v>Surabaya, Indonesia</v>
       </c>
       <c r="J9" t="str">
-        <v>Q2</v>
+        <v>Q4</v>
       </c>
       <c r="K9">
-        <v>24000000000</v>
+        <v>9700000000</v>
       </c>
       <c r="L9">
-        <v>3600000000</v>
+        <v>1100000000</v>
       </c>
       <c r="M9" t="str">
-        <v>Improves RTO from 8 hours to 2 hours.</v>
+        <v>Supports the planned syariah business unit.</v>
       </c>
     </row>
     <row r="10">
@@ -788,13 +788,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Core Banking Server Refresh</v>
+        <v>DRC Site Relocation — Surabaya</v>
       </c>
       <c r="C10" t="str">
-        <v>Replace end-of-life core banking compute and storage.</v>
+        <v>Move the disaster recovery site to a Tier III facility.</v>
       </c>
       <c r="D10" t="str">
-        <v>Servers and/or platforms</v>
+        <v>Data Center / Disaster Recovery Center</v>
       </c>
       <c r="E10" t="str">
         <v>new</v>
@@ -812,16 +812,16 @@
         <v>Surabaya, Indonesia</v>
       </c>
       <c r="J10" t="str">
-        <v>Q3</v>
+        <v>Q2</v>
       </c>
       <c r="K10">
-        <v>18500000000</v>
+        <v>24000000000</v>
       </c>
       <c r="L10">
-        <v>2100000000</v>
+        <v>3600000000</v>
       </c>
       <c r="M10" t="str">
-        <v>Hardware reaches end of support in 2027.</v>
+        <v>Improves RTO from 8 hours to 2 hours.</v>
       </c>
     </row>
     <row r="11">
@@ -829,13 +829,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>SD-WAN Branch Network</v>
+        <v>Core Banking Server Refresh</v>
       </c>
       <c r="C11" t="str">
-        <v>Replace MPLS branch links with SD-WAN across 214 branches.</v>
+        <v>Replace end-of-life core banking compute and storage.</v>
       </c>
       <c r="D11" t="str">
-        <v>Data communication network</v>
+        <v>Servers and/or platforms</v>
       </c>
       <c r="E11" t="str">
         <v>new</v>
@@ -844,7 +844,7 @@
         <v>PPJTI</v>
       </c>
       <c r="G11" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="H11" t="str">
         <v>Jakarta, Indonesia</v>
@@ -853,16 +853,16 @@
         <v>Surabaya, Indonesia</v>
       </c>
       <c r="J11" t="str">
-        <v>Q1</v>
+        <v>Q3</v>
       </c>
       <c r="K11">
-        <v>15200000000</v>
+        <v>18500000000</v>
       </c>
       <c r="L11">
-        <v>4800000000</v>
+        <v>2100000000</v>
       </c>
       <c r="M11" t="str">
-        <v>Related party: network services subsidiary.</v>
+        <v>Hardware reaches end of support in 2027.</v>
       </c>
     </row>
     <row r="12">
@@ -870,13 +870,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Next-Gen Firewall &amp; SIEM Upgrade</v>
+        <v>SD-WAN Branch Network</v>
       </c>
       <c r="C12" t="str">
-        <v>Perimeter firewall replacement and SIEM correlation rebuild.</v>
+        <v>Replace MPLS branch links with SD-WAN across 214 branches.</v>
       </c>
       <c r="D12" t="str">
-        <v>Security systems</v>
+        <v>Data communication network</v>
       </c>
       <c r="E12" t="str">
         <v>new</v>
@@ -885,7 +885,7 @@
         <v>PPJTI</v>
       </c>
       <c r="G12" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="H12" t="str">
         <v>Jakarta, Indonesia</v>
@@ -894,16 +894,16 @@
         <v>Surabaya, Indonesia</v>
       </c>
       <c r="J12" t="str">
-        <v>Q4</v>
+        <v>Q1</v>
       </c>
       <c r="K12">
-        <v>11300000000</v>
+        <v>15200000000</v>
       </c>
       <c r="L12">
-        <v>2700000000</v>
+        <v>4800000000</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>Related party: network services subsidiary.</v>
       </c>
     </row>
     <row r="13">
@@ -911,16 +911,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Primary Data Center Jakarta</v>
+        <v>Next-Gen Firewall &amp; SIEM Upgrade</v>
       </c>
       <c r="C13" t="str">
-        <v>Add two floors of rack capacity to the existing facility.</v>
+        <v>Perimeter firewall replacement and SIEM correlation rebuild.</v>
       </c>
       <c r="D13" t="str">
-        <v>Data Center / Disaster Recovery Center</v>
+        <v>Security systems</v>
       </c>
       <c r="E13" t="str">
-        <v>upgrade</v>
+        <v>new</v>
       </c>
       <c r="F13" t="str">
         <v>PPJTI</v>
@@ -935,16 +935,16 @@
         <v>Surabaya, Indonesia</v>
       </c>
       <c r="J13" t="str">
-        <v>Q3</v>
+        <v>Q4</v>
       </c>
       <c r="K13">
-        <v>7400000000</v>
+        <v>11300000000</v>
       </c>
       <c r="L13">
-        <v>1900000000</v>
+        <v>2700000000</v>
       </c>
       <c r="M13" t="str">
-        <v>Existing DC; not an LKPTI item.</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -952,22 +952,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Legacy Teller Application</v>
+        <v>Primary Data Center Jakarta</v>
       </c>
       <c r="C14" t="str">
-        <v>Branch teller front-end modernisation.</v>
+        <v>Add two floors of rack capacity to the existing facility.</v>
       </c>
       <c r="D14" t="str">
-        <v>Internal management</v>
+        <v>Data Center / Disaster Recovery Center</v>
       </c>
       <c r="E14" t="str">
         <v>upgrade</v>
       </c>
       <c r="F14" t="str">
-        <v>inhouse</v>
+        <v>PPJTI</v>
       </c>
       <c r="G14" t="str">
-        <v>n/a</v>
+        <v>no</v>
       </c>
       <c r="H14" t="str">
         <v>Jakarta, Indonesia</v>
@@ -979,18 +979,59 @@
         <v>Q3</v>
       </c>
       <c r="K14">
+        <v>7400000000</v>
+      </c>
+      <c r="L14">
+        <v>1900000000</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Existing DC; not an LKPTI item.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Legacy Teller Application</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Branch teller front-end modernisation.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Internal management</v>
+      </c>
+      <c r="E15" t="str">
+        <v>upgrade</v>
+      </c>
+      <c r="F15" t="str">
+        <v>inhouse</v>
+      </c>
+      <c r="G15" t="str">
+        <v>n/a</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Jakarta, Indonesia</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Surabaya, Indonesia</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Q3</v>
+      </c>
+      <c r="K15">
         <v>2900000000</v>
       </c>
-      <c r="L14">
+      <c r="L15">
         <v>640000000</v>
       </c>
-      <c r="M14" t="str">
+      <c r="M15" t="str">
         <v>Not present in the 2026 LKPTI — needs a target.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M15"/>
   </ignoredErrors>
 </worksheet>
 </file>